--- a/Cocktail_Test.xlsx
+++ b/Cocktail_Test.xlsx
@@ -1,43 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="392">
-  <si>
-    <t xml:space="preserve">Cocktail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spirituose</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
+  <si>
+    <t>Cocktail</t>
+  </si>
+  <si>
+    <t>Spirituose</t>
   </si>
   <si>
     <t xml:space="preserve">Alkoholische Aromazutat</t>
   </si>
   <si>
-    <t xml:space="preserve">Verlängerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frucht</t>
+    <t>Verlängerer</t>
+  </si>
+  <si>
+    <t>Filler</t>
+  </si>
+  <si>
+    <t>Frucht</t>
   </si>
   <si>
     <t xml:space="preserve">sonstige Zutaten</t>
@@ -46,28 +43,31 @@
     <t xml:space="preserve">Eis </t>
   </si>
   <si>
-    <t xml:space="preserve">Kategorie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blackberry Mint Julip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bourbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caipirinha</t>
+    <t>Kategorie</t>
+  </si>
+  <si>
+    <t>B52</t>
+  </si>
+  <si>
+    <t>Shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blackberry Mint Julep</t>
+  </si>
+  <si>
+    <t>Bourbon</t>
+  </si>
+  <si>
+    <t>Minze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuckersirup (2cl)</t>
+  </si>
+  <si>
+    <t>Julep</t>
+  </si>
+  <si>
+    <t>Caipirinha</t>
   </si>
   <si>
     <t xml:space="preserve">Cachaca / Rum</t>
@@ -76,10 +76,10 @@
     <t xml:space="preserve">Limette, Zucker</t>
   </si>
   <si>
-    <t xml:space="preserve">Sours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daquiri</t>
+    <t>Sour</t>
+  </si>
+  <si>
+    <t>Daquiri</t>
   </si>
   <si>
     <t xml:space="preserve">weißer Rum (4cl)</t>
@@ -88,19 +88,19 @@
     <t xml:space="preserve">Limettensaft(2TL), Zuckersirup (1TL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gimlet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limettensirup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sours, Shortdrink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Godfather</t>
+    <t>Gimlet</t>
+  </si>
+  <si>
+    <t>Gin</t>
+  </si>
+  <si>
+    <t>Limettensirup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sour, Shortdrink</t>
+  </si>
+  <si>
+    <t>Godfather</t>
   </si>
   <si>
     <t xml:space="preserve">Scotch (1cl); Bourbon (2cl)</t>
@@ -109,10 +109,10 @@
     <t xml:space="preserve">Amaretto (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Digestif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highlander</t>
+    <t>Digestif</t>
+  </si>
+  <si>
+    <t>Highlander</t>
   </si>
   <si>
     <t xml:space="preserve">Scoth (6cl)</t>
@@ -127,10 +127,10 @@
     <t xml:space="preserve">Honig (2EL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaffee, Warn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horseneck</t>
+    <t xml:space="preserve">Kaffee, Hot Drink</t>
+  </si>
+  <si>
+    <t>Horseneck</t>
   </si>
   <si>
     <t xml:space="preserve">Bourbon (5cl)</t>
@@ -142,19 +142,19 @@
     <t xml:space="preserve">Angostura (2Spritzer)</t>
   </si>
   <si>
-    <t xml:space="preserve">Highball</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jagertee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Rotwein)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwarztee</t>
+    <t>Highball</t>
+  </si>
+  <si>
+    <t>Jagertee</t>
+  </si>
+  <si>
+    <t>Rum</t>
+  </si>
+  <si>
+    <t>(Rotwein)</t>
+  </si>
+  <si>
+    <t>Schwarztee</t>
   </si>
   <si>
     <t xml:space="preserve">(Zimt, Nelken, Obstler)</t>
@@ -172,10 +172,10 @@
     <t xml:space="preserve">Sekt (10cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aperitif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LynchburgLimonade</t>
+    <t>Aperitif</t>
+  </si>
+  <si>
+    <t>LynchburgLimonade</t>
   </si>
   <si>
     <t xml:space="preserve">Bourbon (4cl)</t>
@@ -184,31 +184,31 @@
     <t xml:space="preserve">Triple Sec/Orangenlikör (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zitronenlimonade</t>
+    <t>Zitronenlimonade</t>
   </si>
   <si>
     <t xml:space="preserve">Zitronensaft (2cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Longdrink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margarita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tequila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organenlikör</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limettensaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sours, New Orleans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manhattan</t>
+    <t>Longdrink</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>Tequila</t>
+  </si>
+  <si>
+    <t>Organenlikör</t>
+  </si>
+  <si>
+    <t>Limettensaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sour, New Orleans</t>
+  </si>
+  <si>
+    <t>Manhattan</t>
   </si>
   <si>
     <t xml:space="preserve">Wermut rot (2cl)</t>
@@ -217,16 +217,16 @@
     <t xml:space="preserve">Angustura (1 Spritzer)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mexikaner</t>
+    <t>Mexikaner</t>
   </si>
   <si>
     <t xml:space="preserve">Korn (oft auch Wodka, Tequila)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sangria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomatensaft</t>
+    <t>Sangria</t>
+  </si>
+  <si>
+    <t>Tomatensaft</t>
   </si>
   <si>
     <t xml:space="preserve">Salz, Pfeffer, Tabascosauce</t>
@@ -238,28 +238,22 @@
     <t xml:space="preserve">Bourbon (6cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Minzsirup (2cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mojito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soda</t>
+    <t>Mojito</t>
+  </si>
+  <si>
+    <t>Soda</t>
   </si>
   <si>
     <t xml:space="preserve">Limettensaft, Minze, Rohrzucker</t>
   </si>
   <si>
-    <t xml:space="preserve">Penicillin</t>
+    <t>Penicillin</t>
   </si>
   <si>
     <t xml:space="preserve">Scotch (5cl); Islay Whiskey (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zitronensaft (2cl), Honig (2cl), Ingwersirup (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sour</t>
+    <t xml:space="preserve">Zitronensaft (2cl), Honig (2cl), Ingwersirup (1.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Pina Colada</t>
@@ -277,13 +271,13 @@
     <t xml:space="preserve">Prince of Wales</t>
   </si>
   <si>
-    <t xml:space="preserve">Cognac</t>
+    <t>Cognac</t>
   </si>
   <si>
     <t xml:space="preserve">Organenlikör / Madeirawein / Maraschino</t>
   </si>
   <si>
-    <t xml:space="preserve">Sekt</t>
+    <t>Sekt</t>
   </si>
   <si>
     <t xml:space="preserve">Angustura (2 Spritzer)</t>
@@ -292,13 +286,13 @@
     <t xml:space="preserve">Sex on the Beach</t>
   </si>
   <si>
-    <t xml:space="preserve">Wodka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pfirsichlikör</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orangensaft</t>
+    <t>Wodka</t>
+  </si>
+  <si>
+    <t>Pfirsichlikör</t>
+  </si>
+  <si>
+    <t>Orangensaft</t>
   </si>
   <si>
     <t xml:space="preserve">Cranberry Saft</t>
@@ -316,19 +310,16 @@
     <t xml:space="preserve">Scoth (3cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Haselnusslikör (1,5cl)</t>
+    <t xml:space="preserve">Haselnusslikör (1.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Kaffee (Espresso), Sahne</t>
   </si>
   <si>
-    <t xml:space="preserve">Schokoladensirup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaffee, Warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sidecar</t>
+    <t>Schokoladensirup</t>
+  </si>
+  <si>
+    <t>Sidecar</t>
   </si>
   <si>
     <t xml:space="preserve">Weinbrand (Cognac) (4cl)</t>
@@ -340,7 +331,7 @@
     <t xml:space="preserve">Singapur Sling</t>
   </si>
   <si>
-    <t xml:space="preserve">Sling</t>
+    <t>Sling</t>
   </si>
   <si>
     <t xml:space="preserve">Tequila Sunrise</t>
@@ -358,10 +349,10 @@
     <t xml:space="preserve">Longdrink, tropisch</t>
   </si>
   <si>
-    <t xml:space="preserve">Zombi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brauner (4,5cl); Weißer (4,5cl), Overproof Rum (3cl)</t>
+    <t>Zombi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brauner (4.5cl); Weißer (4.5cl), Overproof Rum (3cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Maracuja, Orange, Ananas</t>
@@ -379,10 +370,10 @@
     <t xml:space="preserve">Belgisches Kirsch-Bier (Kriek) (16cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zitronensaft (2,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Außergewöhnliche</t>
+    <t xml:space="preserve">Zitronensaft (2.5cl)</t>
+  </si>
+  <si>
+    <t>Außergewöhnlich</t>
   </si>
   <si>
     <t xml:space="preserve">Le Père Bis</t>
@@ -394,16 +385,16 @@
     <t xml:space="preserve">Holunderblütenlikör (2cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kamillentee</t>
+    <t>Kamillentee</t>
   </si>
   <si>
     <t xml:space="preserve">Honig (2TL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tee, Warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maple &amp; Cardamom</t>
+    <t xml:space="preserve">Tee, Hot Drink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple und Cardamom</t>
   </si>
   <si>
     <t xml:space="preserve">Ahornsirup (1TK), Kardamom (Messerspitze), Angostura (2 Spritzer)</t>
@@ -412,7 +403,7 @@
     <t xml:space="preserve">Quarter Deck</t>
   </si>
   <si>
-    <t xml:space="preserve">Sherry</t>
+    <t>Sherry</t>
   </si>
   <si>
     <t xml:space="preserve">Stone Cold Larceny</t>
@@ -430,22 +421,22 @@
     <t xml:space="preserve">Gin (3cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zitronensaft (1,5cl), Puderzucker (1 BL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mimosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orangenlikör</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seelbach</t>
+    <t xml:space="preserve">Zitronensaft (1.5cl), Puderzucker (1 BL)</t>
+  </si>
+  <si>
+    <t>Mimosa</t>
+  </si>
+  <si>
+    <t>Orangenlikör</t>
+  </si>
+  <si>
+    <t>Seelbach</t>
   </si>
   <si>
     <t xml:space="preserve">Orangenlikör, Bitter</t>
   </si>
   <si>
-    <t xml:space="preserve">Negroni</t>
+    <t>Negroni</t>
   </si>
   <si>
     <t xml:space="preserve">Campari (3cl)</t>
@@ -454,7 +445,7 @@
     <t xml:space="preserve">Wermut (3cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Old Fashioned (?), Aperitif</t>
+    <t xml:space="preserve">Old Fashioned, Aperitif</t>
   </si>
   <si>
     <t xml:space="preserve">Angle Face</t>
@@ -466,19 +457,16 @@
     <t xml:space="preserve">Aperikosenlikör (2cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applejack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calvados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zitronensaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sour, New Orleans</t>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Applejack</t>
+  </si>
+  <si>
+    <t>Calvados</t>
+  </si>
+  <si>
+    <t>Zitronensaft</t>
   </si>
   <si>
     <t xml:space="preserve">Ward Eight</t>
@@ -487,7 +475,7 @@
     <t xml:space="preserve"> Orangensaft (2cl), Granatapfelsirup (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Contessa</t>
+    <t>Contessa</t>
   </si>
   <si>
     <t xml:space="preserve">Gin (2cl)</t>
@@ -520,7 +508,7 @@
     <t xml:space="preserve">Limettensaft (2cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mule</t>
+    <t>Mule</t>
   </si>
   <si>
     <t xml:space="preserve">Paris Mule</t>
@@ -550,7 +538,7 @@
     <t xml:space="preserve">London Mule 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Williams</t>
+    <t>Williams</t>
   </si>
   <si>
     <t xml:space="preserve">Birnenbrand (2cl); weißer Rum (1cl)</t>
@@ -562,10 +550,7 @@
     <t xml:space="preserve">Zitronensaft (1Löffel)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sour, International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spotlight</t>
+    <t>Spotlight</t>
   </si>
   <si>
     <t xml:space="preserve">Gin (1cl)</t>
@@ -586,7 +571,7 @@
     <t xml:space="preserve">Grenadine (1cl), Zitrone (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tampico</t>
+    <t>Tampico</t>
   </si>
   <si>
     <t xml:space="preserve">Orangenlikör (4cl), Campari (2cl)</t>
@@ -595,16 +580,13 @@
     <t xml:space="preserve">Tonic Water (bei Bedarf)</t>
   </si>
   <si>
-    <t xml:space="preserve">Besonders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schmelzwasser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enzian (1,5cl), Klosterlikör (1,5cl), Kirschlikör (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCC</t>
+    <t>Schmelzwasser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enzian (1.5cl), Klosterlikör (1.5cl), Kirschlikör (1.5cl)</t>
+  </si>
+  <si>
+    <t>CCC</t>
   </si>
   <si>
     <t xml:space="preserve">Weinbrand (2cl)</t>
@@ -616,22 +598,22 @@
     <t xml:space="preserve">kalter Kaffee (Mokka) (2cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaffee</t>
+    <t>Kaffee</t>
   </si>
   <si>
     <t xml:space="preserve">Grüne Witwe</t>
   </si>
   <si>
-    <t xml:space="preserve">Gin (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pfefferminzlikör (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wermut  trocken (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eierkaffee</t>
+    <t xml:space="preserve">Gin (1.5cl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pfefferminzlikör (1.5cl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wermut  trocken (1.5cl)</t>
+  </si>
+  <si>
+    <t>Eierkaffee</t>
   </si>
   <si>
     <t xml:space="preserve">Eierlikör (3cl)</t>
@@ -640,7 +622,7 @@
     <t xml:space="preserve">kalter/warmer, starker Kaffee (1/2 Tasse)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bijou</t>
+    <t>Bijou</t>
   </si>
   <si>
     <t xml:space="preserve">Chartreuse (2cl)</t>
@@ -685,7 +667,7 @@
     <t xml:space="preserve">Calvados Martini</t>
   </si>
   <si>
-    <t xml:space="preserve">Admiral</t>
+    <t>Admiral</t>
   </si>
   <si>
     <t xml:space="preserve">Bourbon (2cl)</t>
@@ -700,16 +682,16 @@
     <t xml:space="preserve">Zitrone (Schuss)</t>
   </si>
   <si>
-    <t xml:space="preserve">Short / Highball</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teewodka</t>
+    <t xml:space="preserve">Short, Highball</t>
+  </si>
+  <si>
+    <t>Teewodka</t>
   </si>
   <si>
     <t xml:space="preserve">Teebeutel reinhängen für ca 1/2h</t>
   </si>
   <si>
-    <t xml:space="preserve">Tee</t>
+    <t>Tee</t>
   </si>
   <si>
     <t xml:space="preserve">Rum Cooler</t>
@@ -730,13 +712,13 @@
     <t xml:space="preserve">Orangebitter (1Spritzer)</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasserbombe</t>
+    <t>Wasserbombe</t>
   </si>
   <si>
     <t xml:space="preserve">Weinbrand (3cl); Calvados (2cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Capri</t>
+    <t>Capri</t>
   </si>
   <si>
     <t xml:space="preserve">Weinbrand (3cl)</t>
@@ -760,7 +742,7 @@
     <t xml:space="preserve">Weißwein (4-6cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Apple</t>
+    <t>Apple</t>
   </si>
   <si>
     <t xml:space="preserve">Calvados (3cl); Gin (2cl)</t>
@@ -769,10 +751,10 @@
     <t xml:space="preserve">Zitronensaft (1TL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hurricane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bourbon (1,5cl); Gin (1,5cl)</t>
+    <t>Hurricane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourbon (1.5cl); Gin (1.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Gin Tonic</t>
@@ -799,10 +781,10 @@
     <t xml:space="preserve">Zitronensaft (1EL), Ingwersirup (3EL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sours, Fizz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharisäer</t>
+    <t xml:space="preserve">Sour, Fizz</t>
+  </si>
+  <si>
+    <t>Pharisäer</t>
   </si>
   <si>
     <t xml:space="preserve">brauner Rum (5cl)</t>
@@ -814,7 +796,7 @@
     <t xml:space="preserve">Zucker (3-4TL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Grog</t>
+    <t>Grog</t>
   </si>
   <si>
     <t xml:space="preserve">Rum (2cl)</t>
@@ -826,9 +808,6 @@
     <t xml:space="preserve">Zucker (2TL), Nelke, Anis, Zimtstange</t>
   </si>
   <si>
-    <t xml:space="preserve">Warm</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rüdesheimer Kaffee</t>
   </si>
   <si>
@@ -853,43 +832,46 @@
     <t xml:space="preserve">Lady Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Orangenlikör (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zitronensaft (1,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creole</t>
+    <t xml:space="preserve">Orangenlikör (1.5cl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zitronensaft (1.5cl)</t>
+  </si>
+  <si>
+    <t>Creole</t>
   </si>
   <si>
     <t xml:space="preserve">Kräuter (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Old Fashioned (?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poncha</t>
+    <t xml:space="preserve">Old Fashioned</t>
+  </si>
+  <si>
+    <t>Poncha</t>
   </si>
   <si>
     <t xml:space="preserve">Zucker / Honig (2cl), Zitronensaft (1cl), evtl Organgensaft (2cl)</t>
   </si>
   <si>
+    <t>Sours</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rock Lobster</t>
   </si>
   <si>
     <t xml:space="preserve">Kokosnusskreme, Ananassaft, Banane</t>
   </si>
   <si>
-    <t xml:space="preserve">Grenadinensirup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karibik</t>
+    <t>Grenadinensirup</t>
+  </si>
+  <si>
+    <t>Karibik</t>
   </si>
   <si>
     <t xml:space="preserve">Planters Punch</t>
   </si>
   <si>
-    <t xml:space="preserve">Fruchtsaft</t>
+    <t>Fruchtsaft</t>
   </si>
   <si>
     <t xml:space="preserve">Limettensaft, Gewürze</t>
@@ -937,10 +919,10 @@
     <t xml:space="preserve">Big Bamboo</t>
   </si>
   <si>
-    <t xml:space="preserve">Amaretto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ananassaft</t>
+    <t>Amaretto</t>
+  </si>
+  <si>
+    <t>Ananassaft</t>
   </si>
   <si>
     <t xml:space="preserve">Limettensaft, Zuckersirup</t>
@@ -952,7 +934,7 @@
     <t xml:space="preserve">Passionsfrucht, Banane</t>
   </si>
   <si>
-    <t xml:space="preserve">Grenadienensirup</t>
+    <t>Grenadienensirup</t>
   </si>
   <si>
     <t xml:space="preserve">Manisch Water</t>
@@ -961,7 +943,7 @@
     <t xml:space="preserve">Rum, Tequila</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprite</t>
+    <t>Sprite</t>
   </si>
   <si>
     <t xml:space="preserve">Karibik, Longdrink</t>
@@ -970,7 +952,7 @@
     <t xml:space="preserve">Bizzy Izzy Highball</t>
   </si>
   <si>
-    <t xml:space="preserve">Bourbon (4,5cl)</t>
+    <t xml:space="preserve">Bourbon (4.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Amontillado Sherry (3cl)</t>
@@ -985,13 +967,13 @@
     <t xml:space="preserve">Rum (5cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cosmpolitian</t>
+    <t>Cola</t>
+  </si>
+  <si>
+    <t>Limette</t>
+  </si>
+  <si>
+    <t>Cosmpolitian</t>
   </si>
   <si>
     <t xml:space="preserve">Wodka (6cl)</t>
@@ -1003,7 +985,7 @@
     <t xml:space="preserve">Granberrysaft (3cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">IBF</t>
+    <t>IBF</t>
   </si>
   <si>
     <t xml:space="preserve">Bitter (1BL), Orangenlikör (1TL)</t>
@@ -1024,7 +1006,7 @@
     <t xml:space="preserve">Zitronensaft (1cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lumumba</t>
+    <t>Lumumba</t>
   </si>
   <si>
     <t xml:space="preserve">Weinbrand (5cl)</t>
@@ -1051,13 +1033,13 @@
     <t xml:space="preserve">Limettensaft (3cl), Zitronensaft (6cl), Zucker, Minze</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiki</t>
+    <t>Tiki</t>
   </si>
   <si>
     <t xml:space="preserve">Missionary Downfall</t>
   </si>
   <si>
-    <t xml:space="preserve">Rum (6cl); Pfirsichschnaps (1,5cl)</t>
+    <t xml:space="preserve">Rum (6cl); Pfirsichschnaps (1.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Ananassaft (6cl)</t>
@@ -1066,13 +1048,13 @@
     <t xml:space="preserve">Zitronensaft (2cl), Rohrzucker (1cl), Minze</t>
   </si>
   <si>
-    <t xml:space="preserve">Mulata</t>
+    <t>Mulata</t>
   </si>
   <si>
     <t xml:space="preserve">Rum (6cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Origine</t>
+    <t>Origine</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -1090,7 +1072,7 @@
     <t xml:space="preserve">(kalten) Grün-/Schwarztee (10-15cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Planteur</t>
+    <t>Planteur</t>
   </si>
   <si>
     <t xml:space="preserve">Rum (4cl)</t>
@@ -1105,7 +1087,7 @@
     <t xml:space="preserve">Zitronensaft (2cl), (Minze)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fizz / Highball</t>
+    <t xml:space="preserve">Fizz, Highball</t>
   </si>
   <si>
     <t xml:space="preserve">Blood and Sand</t>
@@ -1120,16 +1102,16 @@
     <t xml:space="preserve">Cherry Sour</t>
   </si>
   <si>
-    <t xml:space="preserve">Affiliate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rum (4,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirschlikör (2,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sherry Fino (2,5cl)</t>
+    <t>Affiliate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rum (4.5cl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirschlikör (2.5cl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sherry Fino (2.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Angostura Bitter (2 Spritzer), Orange Bitter (2 Spritzer)</t>
@@ -1141,25 +1123,25 @@
     <t xml:space="preserve">Kirschlikör (5cl)</t>
   </si>
   <si>
-    <t xml:space="preserve">Camilou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armanac</t>
+    <t>Camilou</t>
+  </si>
+  <si>
+    <t>Armanac</t>
   </si>
   <si>
     <t xml:space="preserve">Brombeerlikör, Orangenlikör</t>
   </si>
   <si>
-    <t xml:space="preserve">Mineralwasser</t>
+    <t>Mineralwasser</t>
   </si>
   <si>
     <t xml:space="preserve">Cap Luc</t>
   </si>
   <si>
-    <t xml:space="preserve">Martini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosmarinsirup</t>
+    <t>Martini</t>
+  </si>
+  <si>
+    <t>Rosmarinsirup</t>
   </si>
   <si>
     <t xml:space="preserve">Kir Normand</t>
@@ -1174,13 +1156,13 @@
     <t xml:space="preserve">Jonannisbeerlikör (2cl) oä</t>
   </si>
   <si>
-    <t xml:space="preserve">C.E.B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calvados (3,5cl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kräuterlikör Benedictine (3,5cl)</t>
+    <t>C.E.B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calvados (3.5cl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kräuterlikör Benedictine (3.5cl)</t>
   </si>
   <si>
     <t xml:space="preserve">Le Normandy</t>
@@ -1201,31 +1183,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1237,82 +1199,514 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+  <a:themeElements>
+    <a:clrScheme name="">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="">
+      <a:majorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:srgbClr val="000000"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:srgbClr val="000000"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="53.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="69.45"/>
+    <col customWidth="1" min="1" max="1" style="1" width="22.300000000000001"/>
+    <col customWidth="1" min="2" max="2" style="1" width="43.159999999999997"/>
+    <col customWidth="1" min="3" max="3" style="1" width="53.729999999999997"/>
+    <col customWidth="1" min="4" max="4" style="1" width="47.009999999999998"/>
+    <col customWidth="1" min="5" max="5" style="1" width="28.789999999999999"/>
+    <col customWidth="1" min="6" max="6" style="1" width="33.659999999999997"/>
+    <col customWidth="1" min="7" max="7" style="1" width="69.450000000000003"/>
+    <col bestFit="1" min="9" max="9" width="22.421875"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.800000000000001">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1735,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12.800000000000001">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1349,241 +1743,247 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="12.800000000000001">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="12.800000000000001">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="12.800000000000001">
       <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" ht="12.800000000000001">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="12.800000000000001">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="12.800000000000001">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" ht="12.800000000000001">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="12.800000000000001">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" ht="12.800000000000001">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="I11" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" ht="12.800000000000001">
       <c r="A12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" ht="12.800000000000001">
+      <c r="A13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" ht="12.800000000000001">
+      <c r="A14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" ht="12.800000000000001">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.800000000000001">
       <c r="A16" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I16" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="12.800000000000001">
       <c r="A17" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1592,1534 +1992,1534 @@
         <v>75</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" ht="12.800000000000001">
       <c r="A20" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="2" t="s">
         <v>78</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="12.800000000000001">
+      <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="1" t="s">
+    </row>
+    <row r="22" ht="12.800000000000001">
+      <c r="A22" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="1" t="s">
+    </row>
+    <row r="23" ht="12.800000000000001">
+      <c r="A23" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="1" t="s">
+    </row>
+    <row r="24" ht="12.800000000000001">
+      <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="I24" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" ht="12.800000000000001">
+      <c r="A25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="G25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" ht="12.800000000000001">
+      <c r="A26" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    </row>
+    <row r="27" ht="12.800000000000001">
+      <c r="A27" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="I27" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="1" t="s">
+    </row>
+    <row r="28" ht="12.800000000000001">
+      <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="1" t="s">
+    </row>
+    <row r="30" ht="12.800000000000001">
+      <c r="A30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="I30" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="1" t="s">
+    </row>
+    <row r="31" ht="12.800000000000001">
+      <c r="A31" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="I31" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G31" s="1" t="s">
+    </row>
+    <row r="32" ht="12.800000000000001">
+      <c r="A32" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="I32" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" ht="12.800000000000001">
+      <c r="A33" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="I33" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" ht="12.800000000000001">
+      <c r="A34" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="B34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="I34" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" ht="12.800000000000001">
+      <c r="A36" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="I36" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" ht="12.800000000000001">
+      <c r="A37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="E37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" ht="12.800000000000001">
+      <c r="A38" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" ht="12.800000000000001">
+      <c r="A39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="I39" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="1" t="s">
+    </row>
+    <row r="40" ht="12.800000000000001">
+      <c r="A40" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="1" t="s">
+    </row>
+    <row r="41" ht="12.800000000000001">
+      <c r="A41" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="I41" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" ht="12.800000000000001">
+      <c r="A42" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="G42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" ht="12.800000000000001">
+      <c r="A43" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="1" t="s">
+    </row>
+    <row r="45" ht="12.800000000000001">
+      <c r="A45" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="I45" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" ht="12.800000000000001">
+      <c r="A47" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E47" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E47" s="1" t="s">
+    </row>
+    <row r="48" ht="12.800000000000001">
+      <c r="A48" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="G48" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" ht="12.800000000000001">
+      <c r="A49" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E49" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" ht="12.800000000000001">
+      <c r="A50" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="B50" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" ht="12.800000000000001">
+      <c r="A51" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="I51" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" ht="12.800000000000001">
+      <c r="A52" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="G52" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G50" s="2" t="s">
+    </row>
+    <row r="53" ht="12.800000000000001">
+      <c r="A53" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="I53" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" ht="12.800000000000001">
+      <c r="A54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="E54" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" ht="12.800000000000001">
+      <c r="A55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="I55" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" ht="12.800000000000001">
+      <c r="A56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="I56" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" ht="12.800000000000001">
+      <c r="A57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="I57" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" ht="12.800000000000001">
+      <c r="A58" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+    </row>
+    <row r="59" ht="12.800000000000001">
+      <c r="A59" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="D59" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I59" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" ht="12.800000000000001">
+      <c r="A60" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="I60" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" ht="12.800000000000001">
+      <c r="A62" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="B62" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="I62" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" ht="12.800000000000001">
+      <c r="A63" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="B63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" s="1" t="s">
+    </row>
+    <row r="64" ht="12.800000000000001">
+      <c r="A64" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="I64" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" ht="12.800000000000001">
+      <c r="A65" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="B65" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="I65" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="66" ht="12.800000000000001">
+      <c r="A66" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I66" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="67" ht="12.800000000000001">
+      <c r="A67" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" ht="12.800000000000001">
+      <c r="A68" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="69" ht="12.800000000000001">
+      <c r="A69" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" ht="12.800000000000001">
+      <c r="A71" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" ht="12.800000000000001">
+      <c r="A72" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="G72" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B71" s="1" t="s">
+    </row>
+    <row r="73" ht="12.800000000000001">
+      <c r="A73" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G73" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" ht="12.800000000000001">
+      <c r="A74" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G72" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="D74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" ht="12.800000000000001">
+      <c r="A75" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="I75" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" ht="12.800000000000001">
+      <c r="A76" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="F76" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="I76" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" ht="12.800000000000001">
+      <c r="A77" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="C77" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" ht="12.800000000000001">
+      <c r="A78" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G76" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="I78" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" ht="12.800000000000001">
+      <c r="A79" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="I79" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" ht="12.800000000000001">
+      <c r="A80" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="B80" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>74</v>
       </c>
       <c r="G80" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="81" ht="12.800000000000001">
+      <c r="A81" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I81" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" ht="12.800000000000001">
+      <c r="A82" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="I82" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" ht="12.800000000000001">
+      <c r="A83" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="E83" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="I83" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" ht="12.800000000000001">
+      <c r="A84" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="I84" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" ht="12.800000000000001">
+      <c r="A86" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G83" s="1" t="s">
+      <c r="B86" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="I83" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="G86" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="I86" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" ht="12.800000000000001">
+      <c r="A87" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="B87" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="D87" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I87" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+    </row>
+    <row r="88" ht="12.800000000000001">
+      <c r="A88" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="B88" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="I86" s="1" t="s">
+    </row>
+    <row r="89" ht="12.800000000000001">
+      <c r="A89" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="90" ht="12.800000000000001">
+      <c r="A90" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="91" ht="12.800000000000001">
+      <c r="A91" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="92" ht="12.800000000000001">
+      <c r="A92" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+      <c r="I92" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G90" s="1" t="s">
+    </row>
+    <row r="93" ht="12.800000000000001">
+      <c r="A93" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="B93" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G91" s="1" t="s">
+      <c r="G93" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="I93" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="94" ht="12.800000000000001">
+      <c r="A94" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="B94" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="I94" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="95" ht="12.800000000000001">
+      <c r="A95" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="G95" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="I95" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="96" ht="12.800000000000001">
+      <c r="A96" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="B96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="I96" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="97" ht="12.800000000000001">
+      <c r="A97" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="I95" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="B97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C96" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="I97" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="98" ht="12.800000000000001">
+      <c r="A98" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="I96" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="G98" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="G97" s="1" t="s">
+    </row>
+    <row r="100" ht="12.800000000000001">
+      <c r="A100" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I97" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+      <c r="B100" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>74</v>
       </c>
       <c r="G100" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" ht="12.800000000000001">
+      <c r="A101" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="102" ht="12.800000000000001">
+      <c r="A102" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="F102" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G102" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="103" ht="12.800000000000001">
+      <c r="A103" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+      <c r="B103" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C102" s="1" t="s">
+    </row>
+    <row r="104" ht="12.800000000000001">
+      <c r="A104" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="B104" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C103" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E103" s="1" t="s">
+    </row>
+    <row r="105" ht="12.800000000000001">
+      <c r="A105" s="1" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C104" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G105" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+    <row r="106" ht="12.800000000000001">
+      <c r="A106" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="G106" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+    <row r="107" ht="12.800000000000001">
+      <c r="A107" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B107" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="F107" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I107" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="108" ht="12.800000000000001">
+      <c r="A108" s="1" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="109" ht="12.800000000000001">
+      <c r="A109" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B108" s="1" t="s">
+    </row>
+    <row r="110" ht="12.800000000000001">
+      <c r="A110" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="B110" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="G110" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="111" ht="12.800000000000001">
+      <c r="A111" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="F111" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="112" ht="12.800000000000001">
+      <c r="A112" s="1" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>74</v>
       </c>
       <c r="G112" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="113" ht="12.800000000000001">
+      <c r="A113" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="114" ht="12.800000000000001">
+      <c r="A114" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="B114" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" ht="12.800000000000001">
+      <c r="A115" s="1" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+      <c r="B115" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C115" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F113" s="1" t="s">
+      <c r="D115" s="2" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="G115" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    </row>
+    <row r="116" ht="12.800000000000001">
+      <c r="A116" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C115" s="1" t="s">
+    </row>
+    <row r="117" ht="12.800000000000001">
+      <c r="A117" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="I117" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="118" ht="12.800000000000001">
+      <c r="A118" s="1" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="E118" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G118" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="I118" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="119" ht="12.800000000000001">
+      <c r="A119" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="I117" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G118" s="1" t="s">
+    </row>
+    <row r="120" ht="12.800000000000001">
+      <c r="A120" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="I118" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+      <c r="B120" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C120" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="E119" s="1" t="s">
+    </row>
+    <row r="121" ht="12.800000000000001">
+      <c r="A121" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="F121" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.05277777777778" bottom="1.05277777777778" header="0.78750000000000009" footer="0.78750000000000009"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
